--- a/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/renewal_calendar.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/renewal_calendar.xlsx
@@ -474,36 +474,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -514,136 +514,136 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10.8</v>
+        <v>6.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7</v>
+        <v>9.6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11.3</v>
+        <v>0.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.5</v>
+        <v>9.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -674,36 +674,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9.300000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.5</v>
+        <v>11.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -714,56 +714,56 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2027-01-30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11.2</v>
+        <v>5.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2027-02-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>11.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -774,96 +774,96 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2027-02-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2027-03-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2027-04-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8.300000000000001</v>
+        <v>3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2027-04-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -874,156 +874,156 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-05-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11.3</v>
+        <v>7.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-06-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-06-17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2027-02-09</t>
+          <t>2027-06-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2027-03-10</t>
+          <t>2027-06-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2027-04-05</t>
+          <t>2027-07-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2027-04-16</t>
+          <t>2027-07-28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10.9</v>
+        <v>8.5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2027-04-29</t>
+          <t>2027-08-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1034,27 +1034,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2027-05-06</t>
+          <t>2027-08-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2027-05-30</t>
+          <t>2027-09-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6.6</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1074,72 +1074,72 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2027-06-08</t>
+          <t>2027-09-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.9</v>
+        <v>11.3</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2027-06-16</t>
+          <t>2027-09-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2027-06-26</t>
+          <t>2027-10-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2027-08-31</t>
+          <t>2027-10-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1154,16 +1154,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2027-09-03</t>
+          <t>2027-11-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1174,76 +1174,76 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2027-09-04</t>
+          <t>2027-12-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2027-09-07</t>
+          <t>2027-12-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2027-09-28</t>
+          <t>2027-12-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2027-12-18</t>
+          <t>2027-12-24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11.4</v>
+        <v>5</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1254,20 +1254,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2027-12-21</t>
+          <t>2027-12-29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
